--- a/data/gravel/Mason Macro 2025.xlsx
+++ b/data/gravel/Mason Macro 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EC8BE9-7461-A14C-89E9-B5D888883638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB80E64-DBC6-1E44-AB2D-8A7F5CC62CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4140" yWindow="780" windowWidth="24660" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="130">
   <si>
     <t>brand</t>
   </si>
@@ -405,6 +405,24 @@
   </si>
   <si>
     <t>Macro</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -757,7 +775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1544,189 +1562,219 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B57" s="1">
-        <v>31.6</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B59" s="1">
-        <v>34</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>47</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B61" s="1">
-        <v>180</v>
+        <v>42</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B62" s="1">
-        <v>180</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>67</v>
+        <v>44</v>
+      </c>
+      <c r="B63" s="1">
+        <v>31.6</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>74</v>
+        <v>46</v>
+      </c>
+      <c r="B65" s="1">
+        <v>34</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B67" s="1">
+        <v>180</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B68" s="1">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B69" s="1">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B70" s="1">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B71" s="1">
-        <v>3</v>
+        <v>52</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
+      </c>
+      <c r="B74" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B75" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B76" s="1">
-        <v>3000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B77" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B81" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B82" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>122</v>
       </c>
     </row>

--- a/data/gravel/Mason Macro 2025.xlsx
+++ b/data/gravel/Mason Macro 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB80E64-DBC6-1E44-AB2D-8A7F5CC62CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9122157-2C19-A749-B0D0-83784EC0CE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4140" yWindow="780" windowWidth="24660" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="133">
   <si>
     <t>brand</t>
   </si>
@@ -347,18 +347,12 @@
     <t>top_tube_actual</t>
   </si>
   <si>
-    <t>https://masoncycles.cc/products/macro-frameset</t>
-  </si>
-  <si>
     <t>Mason</t>
   </si>
   <si>
     <t>seat_tube_ct</t>
   </si>
   <si>
-    <t>a8:f38</t>
-  </si>
-  <si>
     <t>aluminum</t>
   </si>
   <si>
@@ -423,6 +417,21 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>https://masoncycles.cc/shop/categories/Macro</t>
+  </si>
+  <si>
+    <t>100-120</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f40</t>
   </si>
 </sst>
 </file>
@@ -775,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -788,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -796,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -820,15 +829,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -836,7 +845,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -861,7 +870,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>77</v>
@@ -1204,7 +1213,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>93</v>
@@ -1313,368 +1322,383 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>23</v>
+        <v>130</v>
       </c>
       <c r="C32" s="4">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="D32" s="4">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="E32" s="4">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="F32" s="4">
-        <v>700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
+        <v>131</v>
+      </c>
+      <c r="C33" s="4">
+        <v>0</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4">
+        <v>0</v>
+      </c>
+      <c r="F33" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="4">
+        <v>700</v>
+      </c>
+      <c r="D34" s="4">
+        <v>700</v>
+      </c>
+      <c r="E34" s="4">
+        <v>700</v>
+      </c>
+      <c r="F34" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C36" s="4">
         <f>2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
-      <c r="D34" s="4">
-        <f t="shared" ref="D34:F34" si="0">2.4*25.4</f>
+      <c r="D36" s="4">
+        <f t="shared" ref="D36:F36" si="0">2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E36" s="4">
         <f t="shared" si="0"/>
         <v>60.959999999999994</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F36" s="4">
         <f t="shared" si="0"/>
         <v>60.959999999999994</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="1" t="s">
+    <row r="37" spans="1:6">
+      <c r="A37" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C35" s="4">
-        <f>C37</f>
+      <c r="C37" s="4">
+        <f>C39</f>
         <v>162</v>
       </c>
-      <c r="D35" s="4">
-        <f>AVERAGE(D37,C38)</f>
+      <c r="D37" s="4">
+        <f>AVERAGE(D39,C40)</f>
         <v>169</v>
       </c>
-      <c r="E35" s="4">
-        <f t="shared" ref="E35:F35" si="1">AVERAGE(E37,D38)</f>
+      <c r="E37" s="4">
+        <f t="shared" ref="E37:F37" si="1">AVERAGE(E39,D40)</f>
         <v>179</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F37" s="4">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="1" t="s">
+    <row r="38" spans="1:6">
+      <c r="A38" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="4">
-        <f>D35</f>
+      <c r="C38" s="4">
+        <f>D37</f>
         <v>169</v>
       </c>
-      <c r="D36" s="4">
-        <f t="shared" ref="D36:E36" si="2">E35</f>
+      <c r="D38" s="4">
+        <f t="shared" ref="D38:E38" si="2">E37</f>
         <v>179</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E38" s="4">
         <f t="shared" si="2"/>
         <v>187</v>
       </c>
-      <c r="F36" s="4">
-        <f t="shared" ref="F36" si="3">F38</f>
+      <c r="F38" s="4">
+        <f t="shared" ref="F38" si="3">F40</f>
         <v>198</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="1" t="s">
+    <row r="39" spans="1:6">
+      <c r="A39" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C39" s="4">
         <v>162</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D39" s="4">
         <v>168</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E39" s="4">
         <v>178</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F39" s="4">
         <v>186</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" s="4">
-        <v>170</v>
-      </c>
-      <c r="D38" s="4">
-        <v>180</v>
-      </c>
-      <c r="E38" s="4">
-        <v>188</v>
-      </c>
-      <c r="F38" s="4">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="C39" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
+        <v>73</v>
+      </c>
+      <c r="C40" s="4">
+        <v>170</v>
+      </c>
+      <c r="D40" s="4">
+        <v>180</v>
+      </c>
+      <c r="E40" s="4">
+        <v>188</v>
+      </c>
+      <c r="F40" s="4">
+        <v>198</v>
+      </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>110</v>
+      <c r="C41" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>113</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="1" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B47" s="1">
-        <v>2.4</v>
+        <v>32</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B49" s="1">
-        <v>100</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="1">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="1">
-        <v>148</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="1">
-        <v>110</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>124</v>
+        <v>40</v>
+      </c>
+      <c r="B55" s="1">
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
+      </c>
+      <c r="B56" s="1">
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="1">
-        <v>31.6</v>
+        <v>42</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>118</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B65" s="1">
-        <v>34</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B67" s="1">
-        <v>180</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B68" s="1">
-        <v>180</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>67</v>
+        <v>48</v>
+      </c>
+      <c r="B69" s="1">
+        <v>180</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>74</v>
+        <v>49</v>
+      </c>
+      <c r="B70" s="1">
+        <v>180</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>74</v>
@@ -1682,60 +1706,60 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B74" s="1">
-        <v>2</v>
+        <v>53</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B75" s="1">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B76" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B77" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
+      </c>
+      <c r="B78" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
+      </c>
+      <c r="B79" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>67</v>
@@ -1743,39 +1767,55 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B81" s="1">
-        <v>1500</v>
+        <v>60</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B82" s="1">
-        <v>3000</v>
+        <v>61</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="B83" s="1">
+        <v>1500</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>116</v>
+        <v>63</v>
+      </c>
+      <c r="B84" s="1">
+        <v>3000</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>122</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
